--- a/simulations/contribution par process.xlsx
+++ b/simulations/contribution par process.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B485FC27-C5C5-4791-9541-7037E8E719CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F932B81-CE25-4121-9D51-FEDBAC794FF9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6950" xr2:uid="{1BC7C774-926D-45AB-9AA8-82AE4C6921CD}"/>
   </bookViews>
@@ -345,22 +345,22 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-742192.63940444961</c:v>
+                  <c:v>-1165585.3540293616</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-907406.06903514802</c:v>
+                  <c:v>-1310292.0798870679</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-394983.87715279532</c:v>
+                  <c:v>-771035.73470901523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-638355.48375363869</c:v>
+                  <c:v>-1062659.8333238726</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-394983.87715279532</c:v>
+                  <c:v>-771035.73470901523</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-643330.62699404941</c:v>
+                  <c:v>-1061953.8317403812</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -524,7 +524,7 @@
                   <c:v>-544740.82216742123</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-651101.69874275709</c:v>
+                  <c:v>-651101.69874275697</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-248327.39276675429</c:v>
@@ -958,7 +958,7 @@
                   <c:v>-781031.64970779605</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1007040.1972417668</c:v>
+                  <c:v>-1007040.1972417666</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-781031.64970779605</c:v>
@@ -1134,7 +1134,7 @@
                   <c:v>-483581.00663625158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-684134.54392147821</c:v>
+                  <c:v>-684134.54392147798</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-483581.00663625158</c:v>
@@ -3717,8 +3717,13 @@
       <sheetName val="Feuil2"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="2">
+          <cell r="AK2" t="str">
+            <v>HC</v>
+          </cell>
+        </row>
         <row r="3">
           <cell r="AD3">
             <v>-544740.82216742123</v>
@@ -3866,8 +3871,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="3">
+          <cell r="B3">
+            <v>-405095.98916297092</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3882,6 +3893,11 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="3">
+          <cell r="D3">
+            <v>0.15622311715281942</v>
+          </cell>
+        </row>
         <row r="14">
           <cell r="C14">
             <v>39.3762728014812</v>
@@ -3894,7 +3910,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3910,7 +3926,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="AK3">
-            <v>-651101.69874275709</v>
+            <v>-651101.69874275697</v>
           </cell>
           <cell r="AL3">
             <v>-479036.53667522129</v>
@@ -3996,7 +4012,7 @@
             <v>-579266.27008729789</v>
           </cell>
           <cell r="AL4">
-            <v>-684134.54392147821</v>
+            <v>-684134.54392147798</v>
           </cell>
           <cell r="AM4">
             <v>-6.3517927378926764</v>
@@ -4460,7 +4476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90666E9C-5B8E-46A5-AE02-C859809DF435}">
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.453125" customWidth="1"/>
@@ -4554,8 +4570,8 @@
         <v>493366.14681729232</v>
       </c>
       <c r="F3" s="1">
-        <f>H3-C3+D3+G3</f>
-        <v>-742192.63940444961</v>
+        <f>H3-(C3+D3+G3)</f>
+        <v>-1165585.3540293616</v>
       </c>
       <c r="G3" s="3">
         <v>127478.38504464801</v>
@@ -4640,15 +4656,15 @@
         <v>541965.34798615903</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:F10" si="1">H4-C4+D4+G4</f>
-        <v>-907406.06903514802</v>
+        <f>H4-(C4+D4+G4)</f>
+        <v>-1310292.0798870679</v>
       </c>
       <c r="G4" s="3">
         <v>117225.033158152</v>
       </c>
       <c r="H4" s="1">
         <f>[3]results!$AK$3</f>
-        <v>-651101.69874275709</v>
+        <v>-651101.69874275697</v>
       </c>
       <c r="J4" t="s">
         <v>2</v>
@@ -4662,11 +4678,11 @@
         <v>69219.316231060424</v>
       </c>
       <c r="N4" s="1">
-        <f t="shared" ref="N4:N10" si="2">L4+M4</f>
+        <f t="shared" ref="N4:N10" si="1">L4+M4</f>
         <v>336918.36029780458</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4:O10" si="3">Q4-(L4+M4+P4)</f>
+        <f t="shared" ref="O4:O10" si="2">Q4-(L4+M4+P4)</f>
         <v>-913067.65553186717</v>
       </c>
       <c r="P4" s="3">
@@ -4688,11 +4704,11 @@
         <v>0.96868020861655502</v>
       </c>
       <c r="X4" s="1">
-        <f t="shared" ref="X4:X10" si="4">V4+W4</f>
+        <f t="shared" ref="X4:X10" si="3">V4+W4</f>
         <v>3.0982667816985217</v>
       </c>
       <c r="Y4" s="1">
-        <f t="shared" ref="Y4:Y10" si="5">AA4-(Z4+V4+W4)</f>
+        <f t="shared" ref="Y4:Y10" si="4">AA4-(Z4+V4+W4)</f>
         <v>-9.2172455291788218</v>
       </c>
       <c r="Z4" s="3">
@@ -4731,8 +4747,8 @@
         <v>418900.38543195894</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="1"/>
-        <v>-394983.87715279532</v>
+        <f>H6-(C6+D6+G6)</f>
+        <v>-771035.73470901523</v>
       </c>
       <c r="G6" s="3">
         <v>103807.956510302</v>
@@ -4756,11 +4772,11 @@
         <v>69219.316231060424</v>
       </c>
       <c r="N6" s="1">
+        <f t="shared" si="1"/>
+        <v>211445.34985321952</v>
+      </c>
+      <c r="O6" s="1">
         <f t="shared" si="2"/>
-        <v>211445.34985321952</v>
-      </c>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
         <v>-781031.64970779605</v>
       </c>
       <c r="P6" s="3">
@@ -4785,11 +4801,11 @@
         <v>0.96868020861655502</v>
       </c>
       <c r="X6" s="1">
+        <f t="shared" si="3"/>
+        <v>2.4335516669812094</v>
+      </c>
+      <c r="Y6" s="1">
         <f t="shared" si="4"/>
-        <v>2.4335516669812094</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" si="5"/>
         <v>-7.0567998152837825</v>
       </c>
       <c r="Z6" s="2">
@@ -4817,8 +4833,8 @@
         <v>355459.36071926582</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="1"/>
-        <v>-638355.48375363869</v>
+        <f>H7-(C7+D7+G7)</f>
+        <v>-1062659.8333238726</v>
       </c>
       <c r="G7" s="3">
         <v>127934.20251730899</v>
@@ -4839,19 +4855,19 @@
         <v>69219.316231060424</v>
       </c>
       <c r="N7" s="1">
+        <f t="shared" si="1"/>
+        <v>216919.58350920171</v>
+      </c>
+      <c r="O7" s="1">
         <f t="shared" si="2"/>
-        <v>216919.58350920171</v>
-      </c>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>-1007040.1972417668</v>
+        <v>-1007040.1972417666</v>
       </c>
       <c r="P7" s="3">
         <v>105986.069811087</v>
       </c>
       <c r="Q7" s="1">
         <f>[3]results!$AL$4</f>
-        <v>-684134.54392147821</v>
+        <v>-684134.54392147798</v>
       </c>
       <c r="T7" t="s">
         <v>2</v>
@@ -4865,11 +4881,11 @@
         <v>0.96868020861655502</v>
       </c>
       <c r="X7" s="1">
+        <f t="shared" si="3"/>
+        <v>2.5204878693293784</v>
+      </c>
+      <c r="Y7" s="1">
         <f t="shared" si="4"/>
-        <v>2.5204878693293784</v>
-      </c>
-      <c r="Y7" s="1">
-        <f t="shared" si="5"/>
         <v>-9.985516055620554</v>
       </c>
       <c r="Z7" s="3">
@@ -4908,8 +4924,8 @@
         <v>418900.38543195894</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="1"/>
-        <v>-394983.87715279532</v>
+        <f>H9-(C9+D9+G9)</f>
+        <v>-771035.73470901523</v>
       </c>
       <c r="G9" s="3">
         <v>103807.956510302</v>
@@ -4933,11 +4949,11 @@
         <v>69219.316231060424</v>
       </c>
       <c r="N9" s="1">
+        <f t="shared" si="1"/>
+        <v>211445.34985321952</v>
+      </c>
+      <c r="O9" s="1">
         <f t="shared" si="2"/>
-        <v>211445.34985321952</v>
-      </c>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
         <v>-781031.64970779605</v>
       </c>
       <c r="P9" s="3">
@@ -4962,11 +4978,11 @@
         <v>0.96868020861655502</v>
       </c>
       <c r="X9" s="1">
+        <f t="shared" si="3"/>
+        <v>2.4335516669812094</v>
+      </c>
+      <c r="Y9" s="1">
         <f t="shared" si="4"/>
-        <v>2.4335516669812094</v>
-      </c>
-      <c r="Y9" s="1">
-        <f t="shared" si="5"/>
         <v>-7.0567998152837825</v>
       </c>
       <c r="Z9" s="3">
@@ -4994,8 +5010,8 @@
         <v>353378.4107379918</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
-        <v>-643330.62699404941</v>
+        <f>H10-(C10+D10+G10)</f>
+        <v>-1061953.8317403812</v>
       </c>
       <c r="G10" s="3">
         <v>125093.630105358</v>
@@ -5016,11 +5032,11 @@
         <v>69219.316231060424</v>
       </c>
       <c r="N10" s="1">
+        <f t="shared" si="1"/>
+        <v>216898.60349551291</v>
+      </c>
+      <c r="O10" s="1">
         <f t="shared" si="2"/>
-        <v>216898.60349551291</v>
-      </c>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
         <v>-1003578.8973223799</v>
       </c>
       <c r="P10" s="3">
@@ -5042,11 +5058,11 @@
         <v>0.96868020861655502</v>
       </c>
       <c r="X10" s="1">
+        <f t="shared" si="3"/>
+        <v>2.5068183387117622</v>
+      </c>
+      <c r="Y10" s="1">
         <f t="shared" si="4"/>
-        <v>2.5068183387117622</v>
-      </c>
-      <c r="Y10" s="1">
-        <f t="shared" si="5"/>
         <v>-9.9528870241670369</v>
       </c>
       <c r="Z10" s="3">
@@ -5055,6 +5071,12 @@
       <c r="AA10" s="1">
         <f>[3]results!$AM$5</f>
         <v>-6.3578543683243343</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="I15" s="1">
+        <f>E6+F6+G6</f>
+        <v>-248327.39276675429</v>
       </c>
     </row>
   </sheetData>
